--- a/output/pdf_financials_xlsx/PTEC.xlsx
+++ b/output/pdf_financials_xlsx/PTEC.xlsx
@@ -1487,22 +1487,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.63519</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.289855</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.348777</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.156194</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.8540219999999999</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.057127</v>
       </c>
     </row>
     <row r="35">
@@ -1557,22 +1557,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.63519</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.289855</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.348777</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.156194</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.8540219999999999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.057127</v>
       </c>
     </row>
     <row r="37">
@@ -1977,22 +1977,22 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.63519</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.290174</v>
+        <v>0.000319</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.359483</v>
+        <v>0.010706</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.207561</v>
+        <v>0.051367</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.018287</v>
+        <v>0.164265</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.079</v>
+        <v>0.021873</v>
       </c>
     </row>
     <row r="49">
@@ -4537,16 +4537,16 @@
         <v>0</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.023527</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.039201</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.015207</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.036579</v>
       </c>
     </row>
     <row r="125">
@@ -4568,16 +4568,16 @@
         <v>0</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.023527</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.039201</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.015207</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.036579</v>
       </c>
     </row>
     <row r="126">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -9178,7 +9178,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -11644,7 +11648,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -14088,7 +14092,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">

--- a/output/pdf_financials_xlsx/PTEC.xlsx
+++ b/output/pdf_financials_xlsx/PTEC.xlsx
@@ -458,12 +458,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>2018-04</t>
+          <t>2018-07</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>2019-04</t>
+          <t>2019-07</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -620,16 +620,16 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.153282</v>
+        <v>0.322806</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.15224</v>
+        <v>0.191972</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.995014</v>
+        <v>1.013429</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.591522</v>
+        <v>2.606229</v>
       </c>
     </row>
     <row r="8">
@@ -1476,15 +1476,11 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0.06988999999999999</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0.205724</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>1.63519</v>
@@ -1511,15 +1507,11 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>0</v>
@@ -1546,15 +1538,11 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0.06988999999999999</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>0.205724</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>1.63519</v>
@@ -1581,15 +1569,11 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>0</v>
@@ -1616,15 +1600,11 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>0</v>
@@ -1651,15 +1631,11 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>0</v>
@@ -1686,15 +1662,11 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>0</v>
@@ -1721,15 +1693,11 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>0</v>
@@ -1756,15 +1724,11 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>0</v>
@@ -1791,15 +1755,11 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>0</v>
@@ -1826,15 +1786,11 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>0</v>
@@ -1861,15 +1817,11 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>0</v>
@@ -1896,15 +1848,11 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>0</v>
@@ -1931,15 +1879,11 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>0</v>
@@ -1966,15 +1910,11 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -2001,15 +1941,11 @@
           <t xml:space="preserve">  Total Current Assets</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="3" t="n">
+        <v>0.09114</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>0.205724</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>1.63519</v>
@@ -2036,15 +1972,11 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D50" s="3" t="n">
         <v>0</v>
@@ -2071,15 +2003,11 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>0</v>
@@ -2106,15 +2034,11 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D52" s="3" t="n">
         <v>0</v>
@@ -2141,15 +2065,11 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>0</v>
@@ -2176,15 +2096,11 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D54" s="3" t="n">
         <v>0</v>
@@ -2258,15 +2174,11 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
         <v>0</v>
@@ -2293,15 +2205,11 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>0</v>
@@ -2328,15 +2236,11 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D58" s="3" t="n">
         <v>0</v>
@@ -2363,15 +2267,11 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>0</v>
@@ -2398,15 +2298,11 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D60" s="3" t="n">
         <v>0</v>
@@ -2433,15 +2329,11 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>0</v>
@@ -2538,15 +2430,11 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>0</v>
@@ -2573,15 +2461,11 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>0</v>
@@ -2608,15 +2492,11 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D66" s="3" t="n">
         <v>0</v>
@@ -2643,15 +2523,11 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>0.008</v>
@@ -2678,15 +2554,11 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D68" s="3" t="n">
         <v>0.008</v>
@@ -2713,15 +2585,11 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>0</v>
@@ -2748,15 +2616,11 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
         <v>0</v>
@@ -2783,15 +2647,11 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>0</v>
@@ -2818,15 +2678,11 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D72" s="3" t="n">
         <v>0</v>
@@ -2853,15 +2709,11 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>0</v>
@@ -2888,15 +2740,11 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
         <v>0</v>
@@ -2923,15 +2771,11 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>0</v>
@@ -2993,15 +2837,11 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>0</v>
@@ -3028,15 +2868,11 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
         <v>0</v>
@@ -3063,15 +2899,11 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>0</v>
@@ -3145,15 +2977,11 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>0</v>
@@ -3180,15 +3008,11 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
         <v>0</v>
@@ -3215,15 +3039,11 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>0</v>
@@ -3250,15 +3070,11 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
         <v>0</v>
@@ -3285,15 +3101,11 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>0</v>
@@ -3390,15 +3202,11 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>0.230372</v>
       </c>
       <c r="D88" s="3" t="n">
         <v>1.71503</v>
@@ -3425,15 +3233,11 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>0</v>
@@ -3460,15 +3264,11 @@
           <t xml:space="preserve">  Retained Earnings</t>
         </is>
       </c>
-      <c r="B90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B90" s="3" t="n">
+        <v>-0.00886</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>-0.084249</v>
       </c>
       <c r="D90" s="3" t="n">
         <v>-0.128543</v>
@@ -3495,15 +3295,11 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>0</v>
@@ -3530,15 +3326,11 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>0.040703</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
@@ -3565,15 +3357,11 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>0</v>
@@ -3600,15 +3388,11 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>0.09193999999999999</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>0.186826</v>
       </c>
       <c r="D94" s="3" t="n">
         <v>1.62719</v>
@@ -3635,15 +3419,11 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>0</v>
@@ -3670,15 +3450,11 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>0.09193999999999999</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>0.186826</v>
       </c>
       <c r="D96" s="3" t="n">
         <v>1.62719</v>
@@ -4138,10 +3914,10 @@
         <v>-0.003252</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.068726</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.014638</v>
       </c>
     </row>
     <row r="112">
@@ -4885,10 +4661,10 @@
         <v>-0.003252</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.068726</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.014638</v>
       </c>
     </row>
     <row r="135">
@@ -4918,10 +4694,10 @@
         <v>-0.473805</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-1.638841</v>
+        <v>-1.707567</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-3.026848</v>
+        <v>-3.041486</v>
       </c>
     </row>
   </sheetData>
@@ -4935,7 +4711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L204"/>
+  <dimension ref="A1:L212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8187,33 +7963,29 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Net loss</t>
+          <t>Cash $</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0.06988999999999999</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>0.205724</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -8225,44 +7997,50 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="5" t="n">
-        <v>-1.348902</v>
-      </c>
-      <c r="J59" s="5" t="n">
-        <v>-1.02888</v>
-      </c>
-      <c r="K59" s="5" t="n">
-        <v>-1.576609</v>
-      </c>
-      <c r="L59" s="5" t="n">
-        <v>-4.223546</v>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>0.02125</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8279,45 +8057,53 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="5" t="n">
-        <v>0.024666</v>
-      </c>
-      <c r="J60" s="5" t="n">
-        <v>0.029579</v>
-      </c>
-      <c r="K60" s="5" t="n">
-        <v>0.046428</v>
-      </c>
-      <c r="L60" s="5" t="n">
-        <v>0.049111</v>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Interest expense</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Current total</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CurrentAssets</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>0.09114</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>0.205724</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -8329,33 +8115,37 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="5" t="n">
-        <v>0.009920999999999999</v>
-      </c>
-      <c r="J61" s="5" t="n">
-        <v>0.008259000000000001</v>
-      </c>
-      <c r="K61" s="5" t="n">
-        <v>0.026706</v>
-      </c>
-      <c r="L61" s="5" t="n">
-        <v>0.004094</v>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Items not involving cash</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bad debts</t>
+          <t>Accrued payables $</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -8364,10 +8154,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F62" s="5" t="n">
+        <v>0.018898</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -8394,36 +8182,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L62" s="5" t="n">
-        <v>0.030536</v>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Gain on settlement of debt</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share capital (Note 4)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>0.230372</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -8450,29 +8240,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L63" s="5" t="n">
-        <v>0.032715</v>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
+          <t>Reserve (Note 4)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>AdditionalPaidInCapital</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -8480,10 +8272,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F64" s="5" t="n">
+        <v>0.040703</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -8495,45 +8285,53 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="5" t="n">
-        <v>0.238682</v>
-      </c>
-      <c r="J64" s="5" t="n">
-        <v>0.345367</v>
-      </c>
-      <c r="K64" s="5" t="n">
-        <v>0.034802</v>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v>0.648424</v>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fair value adjustment of investment</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Deficit</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>-0.00886</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>-0.084249</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -8550,66 +8348,78 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J65" s="5" t="n">
-        <v>-0.002712</v>
-      </c>
-      <c r="K65" s="5" t="n">
-        <v>-0.007471</v>
-      </c>
-      <c r="L65" s="5" t="n">
-        <v>-0.020377</v>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Amounts receivable</t>
+          <t>Shareholders’ equity total</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>0.09193999999999999</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0.186826</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H66" s="5" t="n">
-        <v>-0.000578</v>
-      </c>
-      <c r="I66" s="5" t="n">
-        <v>0.025906</v>
-      </c>
-      <c r="J66" s="5" t="n">
-        <v>-0.100201</v>
-      </c>
-      <c r="K66" s="5" t="n">
-        <v>0.050776</v>
-      </c>
-      <c r="L66" s="5" t="n">
-        <v>-0.041269</v>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -8620,17 +8430,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Prepaid expense and deposits</t>
+          <t>Net loss</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -8654,16 +8464,16 @@
         </is>
       </c>
       <c r="I67" s="5" t="n">
-        <v>0.146309</v>
+        <v>-1.348902</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>-0.040661</v>
+        <v>-1.02888</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>-0.112898</v>
+        <v>-1.576609</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>0.142392</v>
+        <v>-4.223546</v>
       </c>
     </row>
     <row r="68">
@@ -8674,17 +8484,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Deferred revenue</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ChangeInOtherWorkingCapital</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -8707,21 +8517,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I68" s="5" t="n">
+        <v>0.024666</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>0.008238000000000001</v>
+        <v>0.029579</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>-0.008238000000000001</v>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.046428</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>0.049111</v>
       </c>
     </row>
     <row r="69">
@@ -8732,19 +8538,15 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Amounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -8755,23 +8557,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G69" s="5" t="n">
-        <v>-0.010898</v>
-      </c>
-      <c r="H69" s="5" t="n">
-        <v>0.066442</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I69" s="5" t="n">
-        <v>0.116808</v>
+        <v>0.009920999999999999</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>0.310458</v>
+        <v>0.008259000000000001</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>-0.092337</v>
+        <v>0.026706</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>0.351072</v>
+        <v>0.004094</v>
       </c>
     </row>
     <row r="70">
@@ -8782,19 +8588,15 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cash used in operating activities</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Bad debts</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -8825,11 +8627,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K70" s="5" t="n">
-        <v>-1.638841</v>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L70" s="5" t="n">
-        <v>-3.026848</v>
+        <v>0.030536</v>
       </c>
     </row>
     <row r="71">
@@ -8840,12 +8644,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Purchase of equipment</t>
+          <t>Gain on settlement of debt</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -8874,14 +8678,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J71" s="5" t="n">
-        <v>-0.003252</v>
-      </c>
-      <c r="K71" s="5" t="n">
-        <v>-0.068726</v>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L71" s="5" t="n">
-        <v>-0.014638</v>
+        <v>0.032715</v>
       </c>
     </row>
     <row r="72">
@@ -8892,17 +8700,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cash used in investing activities</t>
+          <t>Share-based compensation</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -8925,21 +8733,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I72" s="5" t="n">
+        <v>0.238682</v>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>0.345367</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>-0.068726</v>
+        <v>0.034802</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>-0.014638</v>
+        <v>0.648424</v>
       </c>
     </row>
     <row r="73">
@@ -8950,19 +8754,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of shares, net of share issuance costs</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
+          <t>Fair value adjustment of investment</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -8973,11 +8773,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G73" s="5" t="n">
-        <v>1.484658</v>
-      </c>
-      <c r="H73" s="5" t="n">
-        <v>0.177588</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -8985,13 +8789,13 @@
         </is>
       </c>
       <c r="J73" s="5" t="n">
-        <v>0.301154</v>
+        <v>-0.002712</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>2.428661</v>
+        <v>-0.007471</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>1.796734</v>
+        <v>-0.020377</v>
       </c>
     </row>
     <row r="74">
@@ -9002,15 +8806,19 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Capital drawn by non-controlling interests</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>Amounts receivable</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -9026,28 +8834,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H74" s="5" t="n">
+        <v>-0.000578</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>0.025906</v>
+      </c>
+      <c r="J74" s="5" t="n">
+        <v>-0.100201</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.030305</v>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.050776</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>-0.041269</v>
       </c>
     </row>
     <row r="75">
@@ -9058,15 +8858,19 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Advances received from promissory notes</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
+          <t>Prepaid expense and deposits</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -9087,23 +8891,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I75" s="5" t="n">
+        <v>0.146309</v>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>-0.040661</v>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>-0.112898</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>1.013849</v>
+        <v>0.142392</v>
       </c>
     </row>
     <row r="76">
@@ -9114,15 +8912,19 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Advance for research and development activities</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>Deferred revenue</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ChangeInOtherWorkingCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -9148,18 +8950,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L76" s="5" t="n">
-        <v>0.47078</v>
+      <c r="J76" s="5" t="n">
+        <v>0.008238000000000001</v>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>-0.008238000000000001</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -9170,17 +8970,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Lease payments</t>
+          <t>Amounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>RepaymentOfDebt</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -9193,27 +8993,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G77" s="5" t="n">
+        <v>-0.010898</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>0.066442</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>-0.023527</v>
+        <v>0.116808</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>-0.039201</v>
+        <v>0.310458</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>-0.015207</v>
+        <v>-0.092337</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>-0.036579</v>
+        <v>0.351072</v>
       </c>
     </row>
     <row r="78">
@@ -9224,17 +9020,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cash provided by financing activities</t>
+          <t>Cash used in operating activities</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -9268,10 +9064,10 @@
         </is>
       </c>
       <c r="K78" s="5" t="n">
-        <v>2.383149</v>
+        <v>-1.638841</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>3.244784</v>
+        <v>-3.026848</v>
       </c>
     </row>
     <row r="79">
@@ -9282,17 +9078,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Effect of foreign exchange on cash</t>
+          <t>Purchase of equipment</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>EffectOfExchangeRateChanges</t>
+          <t>PurchaseOfPPE</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -9315,17 +9111,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="5" t="n">
-        <v>-0.027699</v>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J79" s="5" t="n">
-        <v>0.019269</v>
+        <v>-0.003252</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>0.022246</v>
+        <v>-0.068726</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>-0.000193</v>
+        <v>-0.014638</v>
       </c>
     </row>
     <row r="80">
@@ -9336,17 +9134,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Change in cash</t>
+          <t>Cash used in investing activities</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -9369,17 +9167,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="5" t="n">
-        <v>-0.941078</v>
-      </c>
-      <c r="J80" s="5" t="n">
-        <v>-0.192583</v>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K80" s="5" t="n">
-        <v>0.697828</v>
+        <v>-0.068726</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>0.203105</v>
+        <v>-0.014638</v>
       </c>
     </row>
     <row r="81">
@@ -9395,10 +9197,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cash, beginning</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>Proceeds from issuance of shares, net of share issuance costs</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -9409,27 +9215,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I81" s="5" t="n">
-        <v>1.289855</v>
+      <c r="G81" s="5" t="n">
+        <v>1.484658</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>0.177588</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J81" s="5" t="n">
-        <v>0.348777</v>
+        <v>0.301154</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>0.156194</v>
+        <v>2.428661</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>0.8540219999999999</v>
+        <v>1.796734</v>
       </c>
     </row>
     <row r="82">
@@ -9445,7 +9249,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cash, ending</t>
+          <t>Capital drawn by non-controlling interests</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -9469,17 +9273,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I82" s="5" t="n">
-        <v>0.348777</v>
-      </c>
-      <c r="J82" s="5" t="n">
-        <v>0.156194</v>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K82" s="5" t="n">
-        <v>0.8540219999999999</v>
-      </c>
-      <c r="L82" s="5" t="n">
-        <v>1.057127</v>
+        <v>-0.030305</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -9490,12 +9300,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Settlement of promissory notes for shares and warrants</t>
+          <t>Advances received from promissory notes</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -9535,7 +9345,7 @@
         </is>
       </c>
       <c r="L83" s="5" t="n">
-        <v>-1.013849</v>
+        <v>1.013849</v>
       </c>
     </row>
     <row r="84">
@@ -9546,12 +9356,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cash paid during the year for interest</t>
+          <t>Advance for research and development activities</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -9590,10 +9400,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L84" s="5" t="n">
+        <v>0.47078</v>
       </c>
     </row>
     <row r="85">
@@ -9604,15 +9412,19 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cash paid during the year for taxes</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>Lease payments</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -9634,16 +9446,16 @@
         </is>
       </c>
       <c r="I85" s="5" t="n">
-        <v>0.036323</v>
+        <v>-0.023527</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>0.013062</v>
+        <v>-0.039201</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>0.018976</v>
+        <v>-0.015207</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>0.018751</v>
+        <v>-0.036579</v>
       </c>
     </row>
     <row r="86">
@@ -9654,17 +9466,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items total</t>
+          <t>Cash provided by financing activities</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ChangeInWorkingCapital</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -9677,25 +9489,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G86" s="5" t="n">
-        <v>-0.055192</v>
-      </c>
-      <c r="H86" s="5" t="n">
-        <v>-0.37847</v>
-      </c>
-      <c r="I86" s="5" t="n">
-        <v>-0.640344</v>
-      </c>
-      <c r="J86" s="5" t="n">
-        <v>-0.470553</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-1.638841</v>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.383149</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>3.244784</v>
       </c>
     </row>
     <row r="87">
@@ -9706,17 +9524,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Investing activities total</t>
+          <t>Effect of foreign exchange on cash</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>EffectOfExchangeRateChanges</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -9734,22 +9552,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H87" s="5" t="n">
-        <v>-0.14788</v>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I87" s="5" t="n">
-        <v>-0.264709</v>
+        <v>-0.027699</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>-0.003252</v>
+        <v>0.019269</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>-0.068726</v>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.022246</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>-0.000193</v>
       </c>
     </row>
     <row r="88">
@@ -9765,12 +9583,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Financing activities total</t>
+          <t>Change in cash</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -9783,25 +9601,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G88" s="5" t="n">
-        <v>1.484658</v>
-      </c>
-      <c r="H88" s="5" t="n">
-        <v>0.187588</v>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I88" s="5" t="n">
-        <v>-0.008326</v>
+        <v>-0.941078</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>0.261953</v>
+        <v>-0.192583</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>2.383149</v>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.697828</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>0.203105</v>
       </c>
     </row>
     <row r="89">
@@ -9812,12 +9632,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Share-based remuneration</t>
+          <t>Cash, beginning</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -9842,22 +9662,16 @@
         </is>
       </c>
       <c r="I89" s="5" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.289855</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>0.348777</v>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>0.156194</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>0.8540219999999999</v>
       </c>
     </row>
     <row r="90">
@@ -9868,12 +9682,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Fair value gain on investment</t>
+          <t>Cash, ending</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -9897,23 +9711,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I90" s="5" t="n">
+        <v>0.348777</v>
       </c>
       <c r="J90" s="5" t="n">
-        <v>-0.002712</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.156194</v>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>0.8540219999999999</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>1.057127</v>
       </c>
     </row>
     <row r="91">
@@ -9924,12 +9732,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Gain on acquisition of E&amp;E</t>
+          <t>Settlement of promissory notes for shares and warrants</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -9953,8 +9761,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="5" t="n">
-        <v>-0.018734</v>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -9966,10 +9776,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L91" s="5" t="n">
+        <v>-1.013849</v>
       </c>
     </row>
     <row r="92">
@@ -9980,12 +9788,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Net cash used in acquisition of E&amp;E</t>
+          <t>Cash paid during the year for interest</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -10009,8 +9817,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I92" s="5" t="n">
-        <v>-0.006873</v>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -10036,19 +9846,15 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Purchase of investment</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>PurchaseOfInvestment</t>
-        </is>
-      </c>
+          <t>Cash paid during the year for taxes</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -10070,22 +9876,16 @@
         </is>
       </c>
       <c r="I93" s="5" t="n">
-        <v>-0.25614</v>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.036323</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>0.013062</v>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>0.018976</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>0.018751</v>
       </c>
     </row>
     <row r="94">
@@ -10096,17 +9896,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Purchase of property and equipment</t>
+          <t>Changes in non-cash working capital items total</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>PurchaseOfPPE</t>
+          <t>ChangeInWorkingCapital</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -10119,26 +9919,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G94" s="5" t="n">
+        <v>-0.055192</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>-0.37847</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>-0.001696</v>
+        <v>-0.640344</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>-0.003252</v>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.470553</v>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>-1.638841</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -10154,17 +9948,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Proceed from issuance of shares, net of share issuance costs</t>
+          <t>Investing activities total</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -10182,23 +9976,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H95" s="5" t="n">
+        <v>-0.14788</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>-0.264709</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>0.301154</v>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.003252</v>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>-0.068726</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -10219,12 +10007,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Proceeds from exercise of options</t>
+          <t>Financing activities total</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>IssuanceOfCapitalStock</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -10237,26 +10025,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G96" s="5" t="n">
+        <v>1.484658</v>
       </c>
       <c r="H96" s="5" t="n">
-        <v>0.01</v>
+        <v>0.187588</v>
       </c>
       <c r="I96" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.008326</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>0.261953</v>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>2.383149</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -10272,12 +10054,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Capital contributed by non-controlling interests</t>
+          <t>Share-based remuneration</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -10302,7 +10084,7 @@
         </is>
       </c>
       <c r="I97" s="5" t="n">
-        <v>0.005201</v>
+        <v>0.165</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -10328,19 +10110,15 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Net loss $</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Fair value gain on investment</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -10351,21 +10129,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G98" s="5" t="n">
-        <v>-0.044294</v>
-      </c>
-      <c r="H98" s="5" t="n">
-        <v>-0.444015</v>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J98" s="5" t="n">
+        <v>-0.002712</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -10386,12 +10166,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Gain on acquisition of E&amp;E</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -10410,13 +10190,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H99" s="5" t="n">
-        <v>-0.000319</v>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>-0.018734</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -10447,7 +10227,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Prepaid consideration</t>
+          <t>Net cash used in acquisition of E&amp;E</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -10466,13 +10246,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H100" s="5" t="n">
-        <v>-0.14788</v>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>-0.006873</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -10498,17 +10278,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Effect of foreign exchange on cash                                                              (6,573)</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Change in cash</t>
+          <t>Purchase of investment</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>PurchaseOfInvestment</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10521,16 +10301,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G101" s="5" t="n">
-        <v>1.429466</v>
-      </c>
-      <c r="H101" s="5" t="n">
-        <v>-0.345335</v>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>-0.25614</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -10556,17 +10338,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Effect of foreign exchange on cash                                                              (6,573)</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Purchase of property and equipment</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>PurchaseOfPPE</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10579,21 +10361,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G102" s="5" t="n">
-        <v>0.205724</v>
-      </c>
-      <c r="H102" s="5" t="n">
-        <v>1.63519</v>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>-0.001696</v>
+      </c>
+      <c r="J102" s="5" t="n">
+        <v>-0.003252</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -10614,17 +10396,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Effect of foreign exchange on cash                                                              (6,573)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
+          <t>Proceed from issuance of shares, net of share issuance costs</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>NetOtherFinancingCharges</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10637,21 +10419,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G103" s="5" t="n">
-        <v>1.63519</v>
-      </c>
-      <c r="H103" s="5" t="n">
-        <v>1.289855</v>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J103" s="5" t="n">
+        <v>0.301154</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -10672,39 +10456,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CASH FLOWS USED IN OPERATING ACTIVITIES</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Loss for the period $</t>
+          <t>Proceeds from exercise of options</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E104" s="5" t="n">
-        <v>-0.00886</v>
-      </c>
-      <c r="F104" s="5" t="n">
-        <v>-0.075389</v>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H104" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>0.01</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -10730,26 +10514,24 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Item not affecting cash</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Share-based payments</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Capital contributed by non-controlling interests</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F105" s="5" t="n">
-        <v>0.030076</v>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -10761,10 +10543,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I105" s="5" t="n">
+        <v>0.005201</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -10790,32 +10570,34 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital item</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Accrued payables</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F106" s="5" t="n">
-        <v>0.018898</v>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>-0.044294</v>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>-0.444015</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -10846,34 +10628,32 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital item</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="n">
-        <v>-0.02125</v>
-      </c>
-      <c r="F107" s="5" t="n">
-        <v>0.02125</v>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H107" s="5" t="n">
+        <v>-0.000319</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -10904,34 +10684,32 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital item</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="n">
-        <v>-0.03011</v>
-      </c>
-      <c r="F108" s="5" t="n">
-        <v>-0.005165</v>
+          <t>Prepaid consideration</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H108" s="5" t="n">
+        <v>-0.14788</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -10962,30 +10740,34 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Effect of foreign exchange on cash                                                              (6,573)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Proceeds on issuance of share capital</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F109" s="5" t="n">
-        <v>0.2024</v>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Change in cash</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>1.429466</v>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>-0.345335</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -11016,17 +10798,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Effect of foreign exchange on cash                                                              (6,573)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Share issuance costs</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -11034,18 +10816,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F110" s="5" t="n">
-        <v>-0.061401</v>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>0.205724</v>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>1.63519</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -11076,34 +10856,34 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Effect of foreign exchange on cash                                                              (6,573)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Net cash from financing activities</t>
+          <t>Cash, end of year $</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F111" s="5" t="n">
-        <v>0.140999</v>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>1.63519</v>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>1.289855</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -11134,24 +10914,24 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>CASH FLOWS USED IN OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Change in cash during the period</t>
+          <t>Loss for the period $</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0.06988999999999999</v>
+        <v>-0.00886</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>0.135834</v>
+        <v>-0.075389</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -11192,17 +10972,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Item not affecting cash</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Cash, beginning of period</t>
+          <t>Share-based payments</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -11211,7 +10991,7 @@
         </is>
       </c>
       <c r="F113" s="5" t="n">
-        <v>0.06988999999999999</v>
+        <v>0.030076</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -11252,24 +11032,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Change in non-cash working capital item</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Cash, end of period $</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E114" s="5" t="n">
-        <v>0.06988999999999999</v>
+          <t>Accrued payables</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F114" s="5" t="n">
-        <v>0.205724</v>
+        <v>0.018898</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -11310,20 +11088,24 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Change in non-cash working capital item</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>There were no non-cash transactions for the period ended July</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
+          <t>Prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E115" s="5" t="n">
-        <v>0.002018</v>
+        <v>-0.02125</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.02125</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -11359,33 +11141,29 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Note                     Note 19)</t>
+          <t>Change in non-cash working capital item</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Revenue 9</t>
+          <t>Net cash used in operating activities</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>-0.03011</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>-0.005165</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -11407,39 +11185,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K116" s="5" t="n">
-        <v>0.664027</v>
-      </c>
-      <c r="L116" s="5" t="n">
-        <v>0.370424</v>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Advisory and consulting 8</t>
+          <t>Proceeds on issuance of share capital</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E117" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>0.2024</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -11456,42 +11234,50 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J117" s="5" t="n">
-        <v>0.306559</v>
-      </c>
-      <c r="K117" s="5" t="n">
-        <v>0.565215</v>
-      </c>
-      <c r="L117" s="5" t="n">
-        <v>0.458171</v>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bad debts</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr"/>
+          <t>Share issuance costs</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F118" s="5" t="n">
+        <v>-0.061401</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -11518,40 +11304,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L118" s="5" t="n">
-        <v>0.030536</v>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Depreciation 6</t>
+          <t>Net cash from financing activities</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>0.140999</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -11568,42 +11352,48 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J119" s="5" t="n">
-        <v>0.029579</v>
-      </c>
-      <c r="K119" s="5" t="n">
-        <v>0.046428</v>
-      </c>
-      <c r="L119" s="5" t="n">
-        <v>0.049111</v>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Directors' fees 8</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Change in cash during the period</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>0.06988999999999999</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>0.135834</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -11620,35 +11410,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J120" s="5" t="n">
-        <v>0.039732</v>
-      </c>
-      <c r="K120" s="5" t="n">
-        <v>0.018415</v>
-      </c>
-      <c r="L120" s="5" t="n">
-        <v>0.014707</v>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Interest expense</t>
+          <t>Cash, beginning of period</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11656,10 +11452,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F121" s="5" t="n">
+        <v>0.06988999999999999</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -11676,42 +11470,48 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J121" s="5" t="n">
-        <v>0.008259000000000001</v>
-      </c>
-      <c r="K121" s="5" t="n">
-        <v>0.033179</v>
-      </c>
-      <c r="L121" s="5" t="n">
-        <v>0.019729</v>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Marketing and advertisement</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, end of period $</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>0.06988999999999999</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>0.205724</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -11723,67 +11523,79 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I122" s="5" t="n">
-        <v>0.074882</v>
-      </c>
-      <c r="J122" s="5" t="n">
-        <v>0.024038</v>
-      </c>
-      <c r="K122" s="5" t="n">
-        <v>0.063607</v>
-      </c>
-      <c r="L122" s="5" t="n">
-        <v>0.011584</v>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G123" s="5" t="n">
-        <v>0.032641</v>
-      </c>
-      <c r="H123" s="5" t="n">
-        <v>0.351213</v>
-      </c>
-      <c r="I123" s="5" t="n">
-        <v>0.186214</v>
-      </c>
-      <c r="J123" s="5" t="n">
-        <v>0.259296</v>
-      </c>
-      <c r="K123" s="5" t="n">
-        <v>0.402311</v>
-      </c>
-      <c r="L123" s="5" t="n">
-        <v>0.446545</v>
+          <t>There were no non-cash transactions for the period ended July</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" s="5" t="n">
+        <v>0.002018</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -11794,17 +11606,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Note                     Note 19)</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Regulatory and transfer agent</t>
+          <t>Revenue 9</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11817,23 +11629,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G124" s="5" t="n">
-        <v>0.011471</v>
-      </c>
-      <c r="H124" s="5" t="n">
-        <v>0.059458</v>
-      </c>
-      <c r="I124" s="5" t="n">
-        <v>0.013601</v>
-      </c>
-      <c r="J124" s="5" t="n">
-        <v>0.033116</v>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K124" s="5" t="n">
-        <v>0.052272</v>
+        <v>0.664027</v>
       </c>
       <c r="L124" s="5" t="n">
-        <v>0.056131</v>
+        <v>0.370424</v>
       </c>
     </row>
     <row r="125">
@@ -11849,7 +11669,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Research and development costs 12</t>
+          <t>Advisory and consulting 8</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -11878,18 +11698,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J125" s="5" t="n">
+        <v>0.306559</v>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>0.565215</v>
       </c>
       <c r="L125" s="5" t="n">
-        <v>0.277528</v>
+        <v>0.458171</v>
       </c>
     </row>
     <row r="126">
@@ -11905,14 +11721,10 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Office and administration</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Bad debts</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -11933,17 +11745,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I126" s="5" t="n">
-        <v>0.080677</v>
-      </c>
-      <c r="J126" s="5" t="n">
-        <v>0.093169</v>
-      </c>
-      <c r="K126" s="5" t="n">
-        <v>0.088738</v>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L126" s="5" t="n">
-        <v>0.076123</v>
+        <v>0.030536</v>
       </c>
     </row>
     <row r="127">
@@ -11959,12 +11777,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Salaries and management fees 8</t>
+          <t>Depreciation 6</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11992,16 +11810,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J127" s="5" t="n">
+        <v>0.029579</v>
       </c>
       <c r="K127" s="5" t="n">
-        <v>0.817948</v>
+        <v>0.046428</v>
       </c>
       <c r="L127" s="5" t="n">
-        <v>2.353259</v>
+        <v>0.049111</v>
       </c>
     </row>
     <row r="128">
@@ -12017,10 +11833,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Share-based compensation 7(c),8</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
+          <t>Directors' fees 8</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -12047,13 +11867,13 @@
         </is>
       </c>
       <c r="J128" s="5" t="n">
-        <v>0.345367</v>
+        <v>0.039732</v>
       </c>
       <c r="K128" s="5" t="n">
-        <v>0.034802</v>
+        <v>0.018415</v>
       </c>
       <c r="L128" s="5" t="n">
-        <v>0.648424</v>
+        <v>0.014707</v>
       </c>
     </row>
     <row r="129">
@@ -12069,12 +11889,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Interest expense</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12097,17 +11917,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I129" s="5" t="n">
-        <v>0.072605</v>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J129" s="5" t="n">
-        <v>0.059071</v>
+        <v>0.008259000000000001</v>
       </c>
       <c r="K129" s="5" t="n">
-        <v>0.088328</v>
+        <v>0.033179</v>
       </c>
       <c r="L129" s="5" t="n">
-        <v>0.16214</v>
+        <v>0.019729</v>
       </c>
     </row>
     <row r="130">
@@ -12123,14 +11945,10 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Marketing and advertisement</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -12141,23 +11959,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G130" s="5" t="n">
-        <v>0.044294</v>
-      </c>
-      <c r="H130" s="5" t="n">
-        <v>0.448362</v>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I130" s="5" t="n">
-        <v>1.693247</v>
+        <v>0.074882</v>
       </c>
       <c r="J130" s="5" t="n">
-        <v>1.439228</v>
+        <v>0.024038</v>
       </c>
       <c r="K130" s="5" t="n">
-        <v>2.211243</v>
+        <v>0.063607</v>
       </c>
       <c r="L130" s="5" t="n">
-        <v>4.603988</v>
+        <v>0.011584</v>
       </c>
     </row>
     <row r="131">
@@ -12168,15 +11990,19 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Fair value adjustment of investment</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -12187,29 +12013,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G131" s="5" t="n">
+        <v>0.032641</v>
+      </c>
+      <c r="H131" s="5" t="n">
+        <v>0.351213</v>
+      </c>
+      <c r="I131" s="5" t="n">
+        <v>0.186214</v>
       </c>
       <c r="J131" s="5" t="n">
-        <v>0.002712</v>
+        <v>0.259296</v>
       </c>
       <c r="K131" s="5" t="n">
-        <v>-0.007471</v>
+        <v>0.402311</v>
       </c>
       <c r="L131" s="5" t="n">
-        <v>-0.020377</v>
+        <v>0.446545</v>
       </c>
     </row>
     <row r="132">
@@ -12220,15 +12040,19 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Gain on settlement of debt 7(b)</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>Regulatory and transfer agent</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -12239,33 +12063,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G132" s="5" t="n">
+        <v>0.011471</v>
+      </c>
+      <c r="H132" s="5" t="n">
+        <v>0.059458</v>
+      </c>
+      <c r="I132" s="5" t="n">
+        <v>0.013601</v>
+      </c>
+      <c r="J132" s="5" t="n">
+        <v>0.033116</v>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>0.052272</v>
       </c>
       <c r="L132" s="5" t="n">
-        <v>0.032715</v>
+        <v>0.056131</v>
       </c>
     </row>
     <row r="133">
@@ -12276,19 +12090,15 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Research and development costs 12</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -12314,14 +12124,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J133" s="5" t="n">
-        <v>-0.007986999999999999</v>
-      </c>
-      <c r="K133" s="5" t="n">
-        <v>-0.009544</v>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L133" s="5" t="n">
-        <v>-0.004717</v>
+        <v>0.277528</v>
       </c>
     </row>
     <row r="134">
@@ -12332,17 +12146,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Finance income</t>
+          <t>Office and administration</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12365,19 +12179,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I134" s="5" t="n">
+        <v>0.080677</v>
       </c>
       <c r="J134" s="5" t="n">
-        <v>0.003053</v>
+        <v>0.093169</v>
       </c>
       <c r="K134" s="5" t="n">
-        <v>0.020039</v>
+        <v>0.088738</v>
       </c>
       <c r="L134" s="5" t="n">
-        <v>0.021148</v>
+        <v>0.076123</v>
       </c>
     </row>
     <row r="135">
@@ -12388,15 +12200,19 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Other items total</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
+          <t>Salaries and management fees 8</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -12422,14 +12238,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J135" s="5" t="n">
-        <v>-0.002222</v>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K135" s="5" t="n">
-        <v>0.003024</v>
+        <v>0.817948</v>
       </c>
       <c r="L135" s="5" t="n">
-        <v>0.028769</v>
+        <v>2.353259</v>
       </c>
     </row>
     <row r="136">
@@ -12440,12 +12258,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Net loss before income tax</t>
+          <t>Share-based compensation 7(c),8</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -12474,16 +12292,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J136" s="5" t="n">
+        <v>0.345367</v>
       </c>
       <c r="K136" s="5" t="n">
-        <v>-1.544192</v>
+        <v>0.034802</v>
       </c>
       <c r="L136" s="5" t="n">
-        <v>-4.204795</v>
+        <v>0.648424</v>
       </c>
     </row>
     <row r="137">
@@ -12494,17 +12310,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Income tax expense 14</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12527,21 +12343,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I137" s="5" t="n">
+        <v>0.072605</v>
+      </c>
+      <c r="J137" s="5" t="n">
+        <v>0.059071</v>
       </c>
       <c r="K137" s="5" t="n">
-        <v>-0.032417</v>
+        <v>0.088328</v>
       </c>
       <c r="L137" s="5" t="n">
-        <v>-0.018751</v>
+        <v>0.16214</v>
       </c>
     </row>
     <row r="138">
@@ -12552,17 +12364,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Net loss</t>
+          <t>Expenses total</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12575,29 +12387,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G138" s="5" t="n">
+        <v>0.044294</v>
+      </c>
+      <c r="H138" s="5" t="n">
+        <v>0.448362</v>
+      </c>
+      <c r="I138" s="5" t="n">
+        <v>1.693247</v>
       </c>
       <c r="J138" s="5" t="n">
-        <v>-1.02888</v>
+        <v>1.439228</v>
       </c>
       <c r="K138" s="5" t="n">
-        <v>-1.576609</v>
+        <v>2.211243</v>
       </c>
       <c r="L138" s="5" t="n">
-        <v>-4.223546</v>
+        <v>4.603988</v>
       </c>
     </row>
     <row r="139">
@@ -12608,12 +12414,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Foreign exchange translation</t>
+          <t>Fair value adjustment of investment</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -12643,13 +12449,13 @@
         </is>
       </c>
       <c r="J139" s="5" t="n">
-        <v>0.023842</v>
+        <v>0.002712</v>
       </c>
       <c r="K139" s="5" t="n">
-        <v>0.01133</v>
+        <v>-0.007471</v>
       </c>
       <c r="L139" s="5" t="n">
-        <v>-0.02331</v>
+        <v>-0.020377</v>
       </c>
     </row>
     <row r="140">
@@ -12660,12 +12466,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Comprehensive loss</t>
+          <t>Gain on settlement of debt 7(b)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
@@ -12694,14 +12500,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J140" s="5" t="n">
-        <v>-1.005038</v>
-      </c>
-      <c r="K140" s="5" t="n">
-        <v>-1.565279</v>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L140" s="5" t="n">
-        <v>-4.246856</v>
+        <v>0.032715</v>
       </c>
     </row>
     <row r="141">
@@ -12712,15 +12522,19 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Net income (loss) attributable to</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Shareholders of the Company</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -12747,13 +12561,13 @@
         </is>
       </c>
       <c r="J141" s="5" t="n">
-        <v>-1.03197</v>
+        <v>-0.007986999999999999</v>
       </c>
       <c r="K141" s="5" t="n">
-        <v>-1.615037</v>
+        <v>-0.009544</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>-4.235349</v>
+        <v>-0.004717</v>
       </c>
     </row>
     <row r="142">
@@ -12764,17 +12578,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Net income (loss) attributable to</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Non-controlling interest</t>
+          <t>Finance income</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>MinorityInterests</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12797,17 +12611,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I142" s="5" t="n">
-        <v>-0.000691</v>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J142" s="5" t="n">
-        <v>-0.00309</v>
+        <v>0.003053</v>
       </c>
       <c r="K142" s="5" t="n">
-        <v>-0.038428</v>
+        <v>0.020039</v>
       </c>
       <c r="L142" s="5" t="n">
-        <v>-0.011803</v>
+        <v>0.021148</v>
       </c>
     </row>
     <row r="143">
@@ -12818,12 +12634,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Net income (loss) attributable to</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Net income (loss) attributable to total</t>
+          <t>Other items total</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -12847,17 +12663,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I143" s="5" t="n">
-        <v>-1.348902</v>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J143" s="5" t="n">
-        <v>-1.02888</v>
+        <v>-0.002222</v>
       </c>
       <c r="K143" s="5" t="n">
-        <v>-1.576609</v>
+        <v>0.003024</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>-4.223546</v>
+        <v>0.028769</v>
       </c>
     </row>
     <row r="144">
@@ -12868,12 +12686,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Comprehensive income (loss) attributable to</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Shareholders of the Company</t>
+          <t>Net loss before income tax</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -12908,10 +12726,10 @@
         </is>
       </c>
       <c r="K144" s="5" t="n">
-        <v>-1.578178</v>
+        <v>-1.544192</v>
       </c>
       <c r="L144" s="5" t="n">
-        <v>-4.280194</v>
+        <v>-4.204795</v>
       </c>
     </row>
     <row r="145">
@@ -12922,17 +12740,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Comprehensive income (loss) attributable to</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Non-controlling interest 17</t>
+          <t>Income tax expense 14</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>MinorityInterests</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12966,10 +12784,10 @@
         </is>
       </c>
       <c r="K145" s="5" t="n">
-        <v>-0.012899</v>
+        <v>-0.032417</v>
       </c>
       <c r="L145" s="5" t="n">
-        <v>-0.033338</v>
+        <v>-0.018751</v>
       </c>
     </row>
     <row r="146">
@@ -12980,15 +12798,19 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Comprehensive income (loss) attributable to</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Comprehensive income (loss) attributable to total</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -13014,16 +12836,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J146" s="5" t="n">
+        <v>-1.02888</v>
       </c>
       <c r="K146" s="5" t="n">
-        <v>-1.565279</v>
+        <v>-1.576609</v>
       </c>
       <c r="L146" s="5" t="n">
-        <v>-4.246856</v>
+        <v>-4.223546</v>
       </c>
     </row>
     <row r="147">
@@ -13034,19 +12854,15 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Comprehensive income (loss) attributable to</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Foreign exchange translation</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -13072,16 +12888,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J147" s="5" t="n">
+        <v>0.023842</v>
       </c>
       <c r="K147" s="5" t="n">
-        <v>-5e-08</v>
+        <v>0.01133</v>
       </c>
       <c r="L147" s="5" t="n">
-        <v>-1.1e-07</v>
+        <v>-0.02331</v>
       </c>
     </row>
     <row r="148">
@@ -13092,12 +12906,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding - basic and diluted</t>
+          <t>Comprehensive loss</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -13111,23 +12925,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G148" s="5" t="n">
-        <v>2.024</v>
-      </c>
-      <c r="H148" s="5" t="n">
-        <v>16.541939</v>
-      </c>
-      <c r="I148" s="5" t="n">
-        <v>17.827605</v>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J148" s="5" t="n">
-        <v>18.734913</v>
+        <v>-1.005038</v>
       </c>
       <c r="K148" s="5" t="n">
-        <v>29.564705</v>
+        <v>-1.565279</v>
       </c>
       <c r="L148" s="5" t="n">
-        <v>39.386381</v>
+        <v>-4.246856</v>
       </c>
     </row>
     <row r="149">
@@ -13138,12 +12958,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Net income (loss) attributable to</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>$ 71,244 34,802 11,330 58,160 68,621 18,668 30,000 Total Equity 1,498,975 1,000,000 (70,314) (30,305) (1,576,609) 939,123 1,013,849 1,030,000 624,000 648,424 (4,223,546)</t>
+          <t>Shareholders of the Company</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -13172,16 +12992,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J149" s="5" t="n">
+        <v>-1.03197</v>
       </c>
       <c r="K149" s="5" t="n">
-        <v>0.183989</v>
+        <v>-1.615037</v>
       </c>
       <c r="L149" s="5" t="n">
-        <v>-0.02331</v>
+        <v>-4.235349</v>
       </c>
     </row>
     <row r="150">
@@ -13192,15 +13010,19 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Net income (loss) attributable to</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>- - - - - - - - - - - - 48,143 38,428 4,776 61,042 Non- Interest (30,305) controlling 21,535</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
+          <t>Non-controlling interest</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -13221,21 +13043,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I150" s="5" t="n">
+        <v>-0.000691</v>
+      </c>
+      <c r="J150" s="5" t="n">
+        <v>-0.00309</v>
       </c>
       <c r="K150" s="5" t="n">
-        <v>0.09438000000000001</v>
+        <v>-0.038428</v>
       </c>
       <c r="L150" s="5" t="n">
-        <v>0.011803</v>
+        <v>-0.011803</v>
       </c>
     </row>
     <row r="151">
@@ -13246,12 +13064,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Net income (loss) attributable to</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>- - - - - - - - - - - - - - - Deficit (1,615,037) (4,691,649) (4,245,081)</t>
+          <t>Net income (loss) attributable to total</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -13275,21 +13093,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I151" s="5" t="n">
+        <v>-1.348902</v>
+      </c>
+      <c r="J151" s="5" t="n">
+        <v>-1.02888</v>
       </c>
       <c r="K151" s="5" t="n">
-        <v>-8.936730000000001</v>
+        <v>-1.576609</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>-3.076612</v>
+        <v>-4.223546</v>
       </c>
     </row>
     <row r="152">
@@ -13300,12 +13114,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Comprehensive income (loss) attributable to</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>$ - - - - - - - (882) - - statements. Equity Reserve 609,714 400,000 13,306 34,802 1,057,822 30,824 202,770 (18,803)</t>
+          <t>Shareholders of the Company</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -13340,10 +13154,10 @@
         </is>
       </c>
       <c r="K152" s="5" t="n">
-        <v>1.920155</v>
+        <v>-1.578178</v>
       </c>
       <c r="L152" s="5" t="n">
-        <v>0.648424</v>
+        <v>-4.280194</v>
       </c>
     </row>
     <row r="153">
@@ -13354,15 +13168,19 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>of                                                                                                                                                                                            these</t>
+          <t>Comprehensive income (loss) attributable to</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>of                                                                                                                                                                                            these</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
+          <t>Non-controlling interest 17</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -13393,15 +13211,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K153" s="5" t="n">
+        <v>-0.012899</v>
+      </c>
+      <c r="L153" s="5" t="n">
+        <v>-0.033338</v>
       </c>
     </row>
     <row r="154">
@@ -13412,19 +13226,15 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>_____________________________________________________________________________________</t>
+          <t>Comprehensive income (loss) attributable to</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Revenue 9</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Comprehensive income (loss) attributable to total</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -13450,16 +13260,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J154" s="5" t="n">
-        <v>0.425632</v>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K154" s="5" t="n">
-        <v>0.664027</v>
-      </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.565279</v>
+      </c>
+      <c r="L154" s="5" t="n">
+        <v>-4.246856</v>
       </c>
     </row>
     <row r="155">
@@ -13470,17 +13280,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Comprehensive income (loss) attributable to</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Salaries and benefits</t>
+          <t>Basic and diluted loss per share</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13503,19 +13313,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I155" s="5" t="n">
-        <v>0.193608</v>
-      </c>
-      <c r="J155" s="5" t="n">
-        <v>0.241042</v>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K155" s="5" t="n">
-        <v>0.817948</v>
-      </c>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5e-08</v>
+      </c>
+      <c r="L155" s="5" t="n">
+        <v>-1.1e-07</v>
       </c>
     </row>
     <row r="156">
@@ -13526,19 +13338,15 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Loss before income tax</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Weighted average number of common shares outstanding - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -13549,31 +13357,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G156" s="5" t="n">
+        <v>2.024</v>
+      </c>
+      <c r="H156" s="5" t="n">
+        <v>16.541939</v>
+      </c>
+      <c r="I156" s="5" t="n">
+        <v>17.827605</v>
       </c>
       <c r="J156" s="5" t="n">
-        <v>-1.015818</v>
+        <v>18.734913</v>
       </c>
       <c r="K156" s="5" t="n">
-        <v>-1.544192</v>
-      </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>29.564705</v>
+      </c>
+      <c r="L156" s="5" t="n">
+        <v>39.386381</v>
       </c>
     </row>
     <row r="157">
@@ -13584,19 +13384,15 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Income tax expense 12</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>$ 71,244 34,802 11,330 58,160 68,621 18,668 30,000 Total Equity 1,498,975 1,000,000 (70,314) (30,305) (1,576,609) 939,123 1,013,849 1,030,000 624,000 648,424 (4,223,546)</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -13622,16 +13418,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J157" s="5" t="n">
-        <v>-0.013062</v>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K157" s="5" t="n">
-        <v>-0.032417</v>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.183989</v>
+      </c>
+      <c r="L157" s="5" t="n">
+        <v>-0.02331</v>
       </c>
     </row>
     <row r="158">
@@ -13642,12 +13438,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Comprehensive loss attributable to</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Shareholders of the Company</t>
+          <t>- - - - - - - - - - - - 48,143 38,428 4,776 61,042 Non- Interest (30,305) controlling 21,535</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -13676,16 +13472,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J158" s="5" t="n">
-        <v>-1.009872</v>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K158" s="5" t="n">
-        <v>-1.57444</v>
-      </c>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.09438000000000001</v>
+      </c>
+      <c r="L158" s="5" t="n">
+        <v>0.011803</v>
       </c>
     </row>
     <row r="159">
@@ -13696,19 +13492,15 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Comprehensive loss attributable to</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Non-controlling interest 15</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>MinorityInterests</t>
-        </is>
-      </c>
+          <t>- - - - - - - - - - - - - - - Deficit (1,615,037) (4,691,649) (4,245,081)</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -13734,16 +13526,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J159" s="5" t="n">
-        <v>-0.004834</v>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K159" s="5" t="n">
-        <v>-0.012899</v>
-      </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8.936730000000001</v>
+      </c>
+      <c r="L159" s="5" t="n">
+        <v>-3.076612</v>
       </c>
     </row>
     <row r="160">
@@ -13754,12 +13546,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Comprehensive loss attributable to</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Comprehensive loss attributable to total</t>
+          <t>$ - - - - - - - (882) - - statements. Equity Reserve 609,714 400,000 13,306 34,802 1,057,822 30,824 202,770 (18,803)</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -13783,19 +13575,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I160" s="5" t="n">
-        <v>-1.372556</v>
-      </c>
-      <c r="J160" s="5" t="n">
-        <v>-1.005038</v>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K160" s="5" t="n">
-        <v>-1.561541</v>
-      </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.920155</v>
+      </c>
+      <c r="L160" s="5" t="n">
+        <v>0.648424</v>
       </c>
     </row>
     <row r="161">
@@ -13806,19 +13600,15 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Comprehensive loss attributable to</t>
+          <t>of                                                                                                                                                                                            these</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>of                                                                                                                                                                                            these</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -13839,14 +13629,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I161" s="5" t="n">
-        <v>-8e-08</v>
-      </c>
-      <c r="J161" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
-      </c>
-      <c r="K161" s="5" t="n">
-        <v>-5e-08</v>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
@@ -13867,10 +13663,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>10Revenue</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>Revenue 9</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -13891,16 +13691,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I162" s="5" t="n">
-        <v>0.339345</v>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J162" s="5" t="n">
         <v>0.425632</v>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K162" s="5" t="n">
+        <v>0.664027</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -13921,10 +13721,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Advisory and consulting 4, 9</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
+          <t>Salaries and benefits</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -13946,15 +13750,13 @@
         </is>
       </c>
       <c r="I163" s="5" t="n">
-        <v>0.628867</v>
+        <v>0.193608</v>
       </c>
       <c r="J163" s="5" t="n">
-        <v>0.306559</v>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.241042</v>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>0.817948</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -13970,17 +13772,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Depreciation 7</t>
+          <t>Loss before income tax</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14003,16 +13805,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I164" s="5" t="n">
-        <v>0.024666</v>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J164" s="5" t="n">
-        <v>0.029579</v>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.015818</v>
+      </c>
+      <c r="K164" s="5" t="n">
+        <v>-1.544192</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -14028,15 +13830,19 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Directors' fees 9</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr"/>
+          <t>Income tax expense 12</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -14057,16 +13863,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I165" s="5" t="n">
-        <v>0.169524</v>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J165" s="5" t="n">
-        <v>0.039732</v>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.013062</v>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>-0.032417</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -14082,19 +13888,15 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Comprehensive loss attributable to</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Interest expense 14</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Shareholders of the Company</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -14115,16 +13917,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I166" s="5" t="n">
-        <v>0.009920999999999999</v>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J166" s="5" t="n">
-        <v>0.008259000000000001</v>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.009872</v>
+      </c>
+      <c r="K166" s="5" t="n">
+        <v>-1.57444</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -14140,15 +13942,19 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Comprehensive loss attributable to</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Share-based compensation 8, 9</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr"/>
+          <t>Non-controlling interest 15</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -14169,16 +13975,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I167" s="5" t="n">
-        <v>0.238682</v>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J167" s="5" t="n">
-        <v>0.345367</v>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.004834</v>
+      </c>
+      <c r="K167" s="5" t="n">
+        <v>-0.012899</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -14194,12 +14000,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Comprehensive loss attributable to</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Gain on acquisition of E&amp;E 4</t>
+          <t>Comprehensive loss attributable to total</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -14224,17 +14030,13 @@
         </is>
       </c>
       <c r="I168" s="5" t="n">
-        <v>0.018734</v>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.372556</v>
+      </c>
+      <c r="J168" s="5" t="n">
+        <v>-1.005038</v>
+      </c>
+      <c r="K168" s="5" t="n">
+        <v>-1.561541</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
@@ -14250,15 +14052,19 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Comprehensive loss attributable to</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Fair value gain on investment 6</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr"/>
+          <t>Basic and diluted loss per share</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -14279,18 +14085,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I169" s="5" t="n">
+        <v>-8e-08</v>
       </c>
       <c r="J169" s="5" t="n">
-        <v>0.002712</v>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="K169" s="5" t="n">
+        <v>-5e-08</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -14306,19 +14108,15 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>_____________________________________________________________________________________</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>10Revenue</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -14340,10 +14138,10 @@
         </is>
       </c>
       <c r="I170" s="5" t="n">
-        <v>0.021438</v>
+        <v>0.339345</v>
       </c>
       <c r="J170" s="5" t="n">
-        <v>-0.007986999999999999</v>
+        <v>0.425632</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -14369,14 +14167,10 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Finance income</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Advisory and consulting 4, 9</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -14392,14 +14186,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H171" s="5" t="n">
-        <v>0.004347</v>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I171" s="5" t="n">
-        <v>0.001151</v>
+        <v>0.628867</v>
       </c>
       <c r="J171" s="5" t="n">
-        <v>0.003053</v>
+        <v>0.306559</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -14425,10 +14221,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Net loss before income tax</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
+          <t>Depreciation 7</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -14450,10 +14250,10 @@
         </is>
       </c>
       <c r="I172" s="5" t="n">
-        <v>-1.312579</v>
+        <v>0.024666</v>
       </c>
       <c r="J172" s="5" t="n">
-        <v>-1.015818</v>
+        <v>0.029579</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -14479,12 +14279,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Income tax expense 13</t>
+          <t>Directors' fees 9</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -14508,10 +14308,10 @@
         </is>
       </c>
       <c r="I173" s="5" t="n">
-        <v>-0.036323</v>
+        <v>0.169524</v>
       </c>
       <c r="J173" s="5" t="n">
-        <v>-0.013062</v>
+        <v>0.039732</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -14537,12 +14337,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Net loss</t>
+          <t>Interest expense 14</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -14566,10 +14366,10 @@
         </is>
       </c>
       <c r="I174" s="5" t="n">
-        <v>-1.348902</v>
+        <v>0.009920999999999999</v>
       </c>
       <c r="J174" s="5" t="n">
-        <v>-1.02888</v>
+        <v>0.008259000000000001</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -14590,12 +14390,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Foreign exchange translation</t>
+          <t>Share-based compensation 8, 9</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -14620,10 +14420,10 @@
         </is>
       </c>
       <c r="I175" s="5" t="n">
-        <v>-0.023654</v>
+        <v>0.238682</v>
       </c>
       <c r="J175" s="5" t="n">
-        <v>0.023842</v>
+        <v>0.345367</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
@@ -14644,12 +14444,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Comprehensive loss</t>
+          <t>Gain on acquisition of E&amp;E 4</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -14674,10 +14474,12 @@
         </is>
       </c>
       <c r="I176" s="5" t="n">
-        <v>-1.372556</v>
-      </c>
-      <c r="J176" s="5" t="n">
-        <v>-1.005038</v>
+        <v>0.018734</v>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
@@ -14698,12 +14500,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Net income (loss) attributable to</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Shareholders of the company</t>
+          <t>Fair value gain on investment 6</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -14727,11 +14529,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I177" s="5" t="n">
-        <v>-1.349593</v>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J177" s="5" t="n">
-        <v>-1.03197</v>
+        <v>0.002712</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
@@ -14752,15 +14556,19 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Comprehensive loss attributable to</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Shareholders of the company</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
+          <t>Foreign exchange gain (loss)</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -14782,10 +14590,10 @@
         </is>
       </c>
       <c r="I178" s="5" t="n">
-        <v>-1.368813</v>
+        <v>0.021438</v>
       </c>
       <c r="J178" s="5" t="n">
-        <v>-1.009872</v>
+        <v>-0.007986999999999999</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
@@ -14806,17 +14614,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Comprehensive loss attributable to</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Non-controlling interest</t>
+          <t>Finance income</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>MinorityInterests</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -14834,16 +14642,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H179" s="5" t="n">
+        <v>0.004347</v>
       </c>
       <c r="I179" s="5" t="n">
-        <v>0.003743</v>
+        <v>0.001151</v>
       </c>
       <c r="J179" s="5" t="n">
-        <v>-0.004834</v>
+        <v>0.003053</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
@@ -14864,12 +14670,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>- -                5,201 - - 691  - - - - 3,090 1,744          $                   41,851                                    (4,434) 43,309                                            48,143                                                                                        Interest                                                                                                                                                     Non-controlling</t>
+          <t>Net loss before income tax</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -14893,15 +14699,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I180" s="5" t="n">
+        <v>-1.312579</v>
+      </c>
+      <c r="J180" s="5" t="n">
+        <v>-1.015818</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
@@ -14922,15 +14724,19 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>- - Deficit (572,558) (1,349,593) (1,922,151)</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>Income tax expense 13</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -14952,10 +14758,10 @@
         </is>
       </c>
       <c r="I181" s="5" t="n">
-        <v>-2.954121</v>
+        <v>-0.036323</v>
       </c>
       <c r="J181" s="5" t="n">
-        <v>-1.03197</v>
+        <v>-0.013062</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
@@ -14976,15 +14782,19 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Equity                                                                                                                                                                                                                                                                                                                                  financial         Equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>- - - - - - - - - Capital 1,910,137 17,519 1,927,656 301,154 165,000</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -15006,10 +14816,10 @@
         </is>
       </c>
       <c r="I182" s="5" t="n">
-        <v>2.49681</v>
+        <v>-1.348902</v>
       </c>
       <c r="J182" s="5" t="n">
-        <v>0.103</v>
+        <v>-1.02888</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
@@ -15030,12 +14840,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Advisory and consulting $</t>
+          <t>Foreign exchange translation</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -15054,18 +14864,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H183" s="5" t="n">
-        <v>0.030552</v>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="5" t="n">
+        <v>-0.023654</v>
+      </c>
+      <c r="J183" s="5" t="n">
+        <v>0.023842</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -15086,12 +14894,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Rent and office</t>
+          <t>Comprehensive loss</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -15105,21 +14913,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G184" s="5" t="n">
-        <v>0.000182</v>
-      </c>
-      <c r="H184" s="5" t="n">
-        <v>0.007139</v>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I184" s="5" t="n">
+        <v>-1.372556</v>
+      </c>
+      <c r="J184" s="5" t="n">
+        <v>-1.005038</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
@@ -15140,19 +14948,15 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net income (loss) attributable to</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Net loss $</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Shareholders of the company</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -15163,21 +14967,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G185" s="5" t="n">
-        <v>-0.044294</v>
-      </c>
-      <c r="H185" s="5" t="n">
-        <v>-0.444015</v>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I185" s="5" t="n">
+        <v>-1.349593</v>
+      </c>
+      <c r="J185" s="5" t="n">
+        <v>-1.03197</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
@@ -15198,12 +15002,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Comprehensive loss attributable to</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Foreign exchange translation $</t>
+          <t>Shareholders of the company</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -15222,18 +15026,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H186" s="5" t="n">
-        <v>-0.006573</v>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I186" s="5" t="n">
+        <v>-1.368813</v>
+      </c>
+      <c r="J186" s="5" t="n">
+        <v>-1.009872</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
@@ -15254,17 +15056,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Comprehensive loss attributable to</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
+          <t>Non-controlling interest</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>MinorityInterests</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -15277,21 +15079,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G187" s="5" t="n">
-        <v>-0.044294</v>
-      </c>
-      <c r="H187" s="5" t="n">
-        <v>-0.450588</v>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I187" s="5" t="n">
+        <v>0.003743</v>
+      </c>
+      <c r="J187" s="5" t="n">
+        <v>-0.004834</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
@@ -15312,19 +15114,15 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>- -                5,201 - - 691  - - - - 3,090 1,744          $                   41,851                                    (4,434) 43,309                                            48,143                                                                                        Interest                                                                                                                                                     Non-controlling</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -15335,11 +15133,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G188" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="H188" s="5" t="n">
-        <v>-3e-08</v>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -15370,12 +15172,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>g a 186,826 (15,342) (44,294) 10,000</t>
+          <t>- - Deficit (572,558) (1,349,593) (1,922,151)</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -15389,21 +15191,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G189" s="5" t="n">
-        <v>-0.450588</v>
-      </c>
-      <c r="H189" s="5" t="n">
-        <v>0.177588</v>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I189" s="5" t="n">
+        <v>-2.954121</v>
+      </c>
+      <c r="J189" s="5" t="n">
+        <v>-1.03197</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
@@ -15424,12 +15226,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>Equity                                                                                                                                                                                                                                                                                                                                  financial         Equity</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>P shareholders' 1,500,000</t>
+          <t>- - - - - - - - - Capital 1,910,137 17,519 1,927,656 301,154 165,000</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -15443,21 +15245,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G190" s="5" t="n">
-        <v>1.36419</v>
-      </c>
-      <c r="H190" s="5" t="n">
-        <v>1.62719</v>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I190" s="5" t="n">
+        <v>2.49681</v>
+      </c>
+      <c r="J190" s="5" t="n">
+        <v>0.103</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
@@ -15478,12 +15280,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>$        $                                     Total</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>$        $                                     Total</t>
+          <t>Advisory and consulting $</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -15502,10 +15304,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H191" s="5" t="n">
+        <v>0.030552</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -15536,12 +15336,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>$        $                                     Total</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Deficit (84,249) (44,294) (128,543)</t>
+          <t>Rent and office</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -15556,10 +15356,10 @@
         </is>
       </c>
       <c r="G192" s="5" t="n">
-        <v>-0.572558</v>
+        <v>0.000182</v>
       </c>
       <c r="H192" s="5" t="n">
-        <v>-0.444015</v>
+        <v>0.007139</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -15590,15 +15390,19 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>$        $                                     Total</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>- - - - - - - other loss statements</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr"/>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -15610,10 +15414,10 @@
         </is>
       </c>
       <c r="G193" s="5" t="n">
-        <v>-0.006573</v>
+        <v>-0.044294</v>
       </c>
       <c r="H193" s="5" t="n">
-        <v>-0.006573</v>
+        <v>-0.444015</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -15644,12 +15448,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>$        $                                                                                                                                                                                     part</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>$        $                                                                                                                                                                                     part total</t>
+          <t>Foreign exchange translation $</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -15668,10 +15472,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H194" s="5" t="n">
+        <v>-0.006573</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -15702,15 +15504,19 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>$        $                                                                                                                                                                                     part</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>$        $                                                                                                                                                                                     part integral Amount 230,372 (15,342) 17,519 177,588 an Equity 1,500,000</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -15722,10 +15528,10 @@
         </is>
       </c>
       <c r="G195" s="5" t="n">
-        <v>1.910137</v>
+        <v>-0.044294</v>
       </c>
       <c r="H195" s="5" t="n">
-        <v>1.71503</v>
+        <v>-0.450588</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -15756,30 +15562,34 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Administration $</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr"/>
-      <c r="E196" s="5" t="n">
-        <v>0.000182</v>
-      </c>
-      <c r="F196" s="5" t="n">
-        <v>5.9e-05</v>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G196" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="H196" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -15810,36 +15620,30 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>g</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>g a 186,826 (15,342) (44,294) 10,000</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F197" s="5" t="n">
-        <v>0.029545</v>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G197" s="5" t="n">
+        <v>-0.450588</v>
+      </c>
+      <c r="H197" s="5" t="n">
+        <v>0.177588</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
@@ -15870,12 +15674,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>g</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 4)</t>
+          <t>P shareholders' 1,500,000</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -15884,18 +15688,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F198" s="5" t="n">
-        <v>0.030076</v>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G198" s="5" t="n">
+        <v>1.36419</v>
+      </c>
+      <c r="H198" s="5" t="n">
+        <v>1.62719</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
@@ -15926,24 +15728,24 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>$        $                                     Total</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E199" s="5" t="n">
-        <v>0.008678</v>
-      </c>
-      <c r="F199" s="5" t="n">
-        <v>0.015709</v>
+          <t>$        $                                     Total</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -15984,34 +15786,30 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>$        $                                     Total</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the period $</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E200" s="5" t="n">
-        <v>-0.00886</v>
-      </c>
-      <c r="F200" s="5" t="n">
-        <v>-0.075389</v>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Deficit (84,249) (44,294) (128,543)</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G200" s="5" t="n">
+        <v>-0.572558</v>
+      </c>
+      <c r="H200" s="5" t="n">
+        <v>-0.444015</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
@@ -16042,34 +15840,30 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>$        $                                     Total</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E201" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="F201" s="5" t="n">
-        <v>-5e-08</v>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>- - - - - - - other loss statements</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G201" s="5" t="n">
+        <v>-0.006573</v>
+      </c>
+      <c r="H201" s="5" t="n">
+        <v>-0.006573</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
@@ -16100,24 +15894,24 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>$        $                                                                                                                                                                                     part</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
-      <c r="E202" s="5" t="n">
-        <v>0.444444</v>
-      </c>
-      <c r="F202" s="5" t="n">
-        <v>1.514608</v>
+          <t>$        $                                                                                                                                                                                     part total</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -16158,30 +15952,30 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>-     - - - -                         these</t>
+          <t>$        $                                                                                                                                                                                     part</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>-     - - - -                         these of (8,860) (8,860)</t>
+          <t>$        $                                                                                                                                                                                     part integral Amount 230,372 (15,342) 17,519 177,588 an Equity 1,500,000</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
-      <c r="E203" s="5" t="n">
-        <v>-0.084249</v>
-      </c>
-      <c r="F203" s="5" t="n">
-        <v>-0.075389</v>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G203" s="5" t="n">
+        <v>1.910137</v>
+      </c>
+      <c r="H203" s="5" t="n">
+        <v>1.71503</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -16212,47 +16006,503 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>period                                    year             SHAREHOLDERS’</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>period                                    year             SHAREHOLDERS’ the IN theINC. for for 4)</t>
+          <t>Administration $</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" s="5" t="n">
+        <v>0.000182</v>
+      </c>
+      <c r="F204" s="5" t="n">
+        <v>5.9e-05</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F205" s="5" t="n">
+        <v>0.029545</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Share-based compensation (Note 4)</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F206" s="5" t="n">
+        <v>0.030076</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Transfer agent and filing fees</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="n">
+        <v>0.008678</v>
+      </c>
+      <c r="F207" s="5" t="n">
+        <v>0.015709</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E208" s="5" t="n">
+        <v>-0.00886</v>
+      </c>
+      <c r="F208" s="5" t="n">
+        <v>-0.075389</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E209" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="F209" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="n">
+        <v>0.444444</v>
+      </c>
+      <c r="F210" s="5" t="n">
+        <v>1.514608</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>-     - - - -                         these</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>-     - - - -                         these of (8,860) (8,860)</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" s="5" t="n">
+        <v>-0.084249</v>
+      </c>
+      <c r="F211" s="5" t="n">
+        <v>-0.075389</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>period                                    year             SHAREHOLDERS’</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>period                                    year             SHAREHOLDERS’ the IN theINC. for for 4)</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" s="5" t="n">
         <v>4e-06</v>
       </c>
-      <c r="F204" s="5" t="n">
+      <c r="F212" s="5" t="n">
         <v>4e-06</v>
       </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L204" t="inlineStr">
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
         <is>
           <t>-</t>
         </is>
